--- a/Diploma's.xlsx
+++ b/Diploma's.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hogeschoolpxl-my.sharepoint.com/personal/12503773_student_pxl_be/Documents/Documents/GitHub/portfolio-IlyaTripspxl/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hogeschoolpxl-my.sharepoint.com/personal/12503773_student_pxl_be/Documents/Documents/GitHub/publiek-bestanden-to-share/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{1C982382-5C53-4439-ACB8-1274324A0235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57525DCE-302D-4A9D-8D65-B19A9586BFB9}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{1C982382-5C53-4439-ACB8-1274324A0235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C7B6805-63C8-46FD-AE8B-1D8380494BFD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{6AF239EE-D8A7-419E-8F54-456A39A7C8E4}"/>
   </bookViews>
@@ -107,12 +107,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -121,19 +136,19 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -473,46 +488,46 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="61.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="4">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="5">
         <v>45838</v>
       </c>
     </row>
